--- a/outputs/353-6.xlsx
+++ b/outputs/353-6.xlsx
@@ -257,16 +257,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -486,730 +490,730 @@
   <dimension ref="A1:AH9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="19.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="19.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="U1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="V1" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="W1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="X1" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Y1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="Z1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AC1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AF1" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AG1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AH1" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1154408</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="0" t="s">
+      <c r="K2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L2" s="0" t="s">
+      <c r="L2" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="n">
+      <c r="Q2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="S2" s="0" t="n">
+      <c r="S2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="0" t="n">
+      <c r="T2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U2" s="0" t="n">
+      <c r="U2" s="1" t="n">
         <v>3482459</v>
       </c>
-      <c r="W2" s="2" t="n">
+      <c r="W2" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="Y2" s="0" t="s">
+      <c r="Y2" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" s="0" t="s">
+      <c r="Z2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" s="0" t="s">
+      <c r="AD2" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>1154408</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I3" s="0" t="s">
+      <c r="D3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K3" s="0" t="s">
+      <c r="K3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L3" s="0" t="s">
+      <c r="L3" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="2" t="n">
+      <c r="Q3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="S3" s="0" t="n">
+      <c r="S3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T3" s="0" t="n">
+      <c r="T3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U3" s="0" t="n">
+      <c r="U3" s="1" t="n">
         <v>3482662</v>
       </c>
-      <c r="V3" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" s="2" t="n">
+      <c r="V3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>44470.3405902778</v>
       </c>
-      <c r="X3" s="2" t="n">
+      <c r="X3" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="Y3" s="0" t="s">
+      <c r="Y3" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z3" s="0" t="s">
+      <c r="Z3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA3" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD3" s="0" t="s">
+      <c r="AA3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD3" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG3" s="0" t="n">
+      <c r="AG3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH3" s="0" t="n">
+      <c r="AH3" s="1" t="n">
         <v>0.167</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>1154408</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G4" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I4" s="0" t="s">
+      <c r="D4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="0" t="s">
+      <c r="K4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
+      <c r="Q4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="3" t="n">
         <v>44470.0296180556</v>
       </c>
-      <c r="S4" s="0" t="n">
+      <c r="S4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="T4" s="0" t="n">
+      <c r="T4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="U4" s="0" t="n">
+      <c r="U4" s="1" t="n">
         <v>3482666</v>
       </c>
-      <c r="V4" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W4" s="2" t="n">
+      <c r="V4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W4" s="3" t="n">
         <v>44470.3408796296</v>
       </c>
-      <c r="X4" s="2" t="n">
+      <c r="X4" s="3" t="n">
         <v>44470.3405902778</v>
       </c>
-      <c r="Y4" s="0" t="s">
+      <c r="Y4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z4" s="0" t="s">
+      <c r="Z4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA4" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD4" s="0" t="s">
+      <c r="AA4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG4" s="0" t="n">
+      <c r="AG4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH4" s="0" t="n">
+      <c r="AH4" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>1154409</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="3" t="n">
         <v>44470.0629398148</v>
       </c>
-      <c r="D5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" s="0" t="s">
+      <c r="D5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K5" s="0" t="s">
+      <c r="K5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="3" t="n">
         <v>44470.345787037</v>
       </c>
-      <c r="S5" s="0" t="n">
+      <c r="S5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="0" t="n">
+      <c r="T5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="1" t="n">
         <v>3482685</v>
       </c>
-      <c r="V5" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W5" s="2" t="n">
+      <c r="V5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W5" s="3" t="n">
         <v>44470.3432060185</v>
       </c>
-      <c r="X5" s="2" t="n">
+      <c r="X5" s="3" t="n">
         <v>44470.0629398148</v>
       </c>
-      <c r="Y5" s="0" t="s">
+      <c r="Y5" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z5" s="0" t="s">
+      <c r="Z5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA5" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD5" s="0" t="s">
+      <c r="AA5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD5" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG5" s="0" t="n">
+      <c r="AG5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH5" s="0" t="n">
+      <c r="AH5" s="1" t="n">
         <v>0.233</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>1154409</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="3" t="n">
         <v>44470.0629398148</v>
       </c>
-      <c r="D6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I6" s="0" t="s">
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K6" s="0" t="s">
+      <c r="K6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" s="2" t="n">
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="3" t="n">
         <v>44470.345787037</v>
       </c>
-      <c r="S6" s="0" t="n">
+      <c r="S6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="0" t="n">
+      <c r="T6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="1" t="n">
         <v>3482699</v>
       </c>
-      <c r="V6" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W6" s="2" t="n">
+      <c r="V6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>44470.3455671296</v>
       </c>
-      <c r="X6" s="2" t="n">
+      <c r="X6" s="3" t="n">
         <v>44470.3432060185</v>
       </c>
-      <c r="Y6" s="0" t="s">
+      <c r="Y6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z6" s="0" t="s">
+      <c r="Z6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA6" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD6" s="0" t="s">
+      <c r="AA6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG6" s="0" t="n">
+      <c r="AG6" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH6" s="0" t="n">
+      <c r="AH6" s="1" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>1154409</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="3" t="n">
         <v>44470.0629398148</v>
       </c>
-      <c r="D7" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I7" s="0" t="s">
+      <c r="D7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="0" t="s">
+      <c r="J7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="0" t="s">
+      <c r="K7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="2" t="n">
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="3" t="n">
         <v>44470.345787037</v>
       </c>
-      <c r="S7" s="0" t="n">
+      <c r="S7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="0" t="n">
+      <c r="T7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="1" t="n">
         <v>3482701</v>
       </c>
-      <c r="V7" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W7" s="2" t="n">
+      <c r="V7" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>44470.345787037</v>
       </c>
-      <c r="X7" s="2" t="n">
+      <c r="X7" s="3" t="n">
         <v>44470.3455671296</v>
       </c>
-      <c r="Y7" s="0" t="s">
+      <c r="Y7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z7" s="0" t="s">
+      <c r="Z7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA7" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB7" s="0" t="s">
+      <c r="AA7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AB7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="AD7" s="0" t="s">
+      <c r="AD7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="AE7" s="0" t="s">
+      <c r="AE7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AF7" s="0" t="s">
+      <c r="AF7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AG7" s="0" t="n">
+      <c r="AG7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH7" s="0" t="n">
+      <c r="AH7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>1154414</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="3" t="n">
         <v>44470.2605324074</v>
       </c>
-      <c r="D8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G8" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H8" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" s="0" t="s">
+      <c r="D8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J8" s="0" t="s">
+      <c r="J8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K8" s="0" t="s">
+      <c r="K8" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R8" s="2" t="n">
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="3" t="n">
         <v>44470.3162268519</v>
       </c>
-      <c r="S8" s="0" t="n">
+      <c r="S8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="0" t="n">
+      <c r="T8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="1" t="n">
         <v>3482465</v>
       </c>
-      <c r="V8" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W8" s="2" t="n">
+      <c r="V8" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>44470.2605324074</v>
       </c>
-      <c r="Y8" s="0" t="s">
+      <c r="Y8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z8" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="AA8" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD8" s="0" t="s">
+      <c r="Z8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AA8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD8" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>1154414</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>12345678</v>
       </c>
-      <c r="C9" s="2" t="n">
+      <c r="C9" s="3" t="n">
         <v>44470.2605324074</v>
       </c>
-      <c r="D9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="H9" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="I9" s="0" t="s">
+      <c r="D9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="J9" s="0" t="s">
+      <c r="J9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="K9" s="0" t="s">
+      <c r="K9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="Q9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="2" t="n">
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="3" t="n">
         <v>44470.3162268519</v>
       </c>
-      <c r="S9" s="0" t="n">
+      <c r="S9" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="T9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="0" t="n">
+      <c r="T9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="1" t="n">
         <v>3482509</v>
       </c>
-      <c r="V9" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="W9" s="2" t="n">
+      <c r="V9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="W9" s="3" t="n">
         <v>44470.3159375</v>
       </c>
-      <c r="X9" s="2" t="n">
+      <c r="X9" s="3" t="n">
         <v>44470.2605324074</v>
       </c>
-      <c r="Y9" s="0" t="s">
+      <c r="Y9" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="Z9" s="0" t="s">
+      <c r="Z9" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA9" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD9" s="0" t="s">
+      <c r="AA9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="AG9" s="0" t="n">
+      <c r="AG9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="AH9" s="0" t="n">
+      <c r="AH9" s="1" t="n">
         <v>0.417</v>
       </c>
     </row>
